--- a/diseases/d165/1995-1999.xlsx
+++ b/diseases/d165/1995-1999.xlsx
@@ -11693,6 +11693,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12228,6 +12233,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12763,6 +12773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13298,6 +13313,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13833,6 +13853,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14368,6 +14393,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14903,6 +14933,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15438,6 +15473,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15973,6 +16013,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16508,6 +16553,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17043,6 +17093,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17578,6 +17633,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18503,6 +18563,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19038,6 +19103,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19573,6 +19643,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20108,6 +20183,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20643,6 +20723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21178,6 +21263,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21713,6 +21803,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22248,6 +22343,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22783,6 +22883,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23318,6 +23423,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23853,6 +23963,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24388,6 +24503,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25313,6 +25433,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25848,6 +25973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26383,6 +26513,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26918,6 +27053,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27453,6 +27593,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27988,6 +28133,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28523,6 +28673,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29058,6 +29213,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29593,6 +29753,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30128,6 +30293,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30663,6 +30833,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31196,6 +31371,11 @@
       <c r="S167" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">

--- a/diseases/d165/1995-1999.xlsx
+++ b/diseases/d165/1995-1999.xlsx
@@ -11688,6 +11688,11 @@
       <c r="Q58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11700,13 +11705,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12213,6 +12228,11 @@
       <c r="Q61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12225,13 +12245,23 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12738,6 +12768,11 @@
       <c r="Q64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12750,13 +12785,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -13263,6 +13308,11 @@
       <c r="Q67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13275,13 +13325,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -13788,6 +13848,11 @@
       <c r="Q70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13800,13 +13865,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14313,6 +14388,11 @@
       <c r="Q73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14325,13 +14405,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14838,6 +14928,11 @@
       <c r="Q76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14850,13 +14945,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -15363,6 +15468,11 @@
       <c r="Q79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15375,13 +15485,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -15888,6 +16008,11 @@
       <c r="Q82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15900,13 +16025,23 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -16413,6 +16548,11 @@
       <c r="Q85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16425,13 +16565,23 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -16938,6 +17088,11 @@
       <c r="Q88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16950,13 +17105,23 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -17463,6 +17628,11 @@
       <c r="Q91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17475,13 +17645,23 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV91" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -18378,6 +18558,11 @@
       <c r="Q96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18390,13 +18575,23 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
       </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV96" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -18903,6 +19098,11 @@
       <c r="Q99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18915,13 +19115,23 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
       </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV99" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -19428,6 +19638,11 @@
       <c r="Q102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19440,13 +19655,23 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
       </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV102" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -19953,6 +20178,11 @@
       <c r="Q105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19965,13 +20195,23 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
       </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV105" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -20478,6 +20718,11 @@
       <c r="Q108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20490,13 +20735,23 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
       </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV108" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -21003,6 +21258,11 @@
       <c r="Q111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21015,13 +21275,23 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV111" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -21528,6 +21798,11 @@
       <c r="Q114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21540,13 +21815,23 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
       </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV114" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22053,6 +22338,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22065,13 +22355,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22578,6 +22878,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22590,13 +22895,23 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV120" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23103,6 +23418,11 @@
       <c r="Q123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23115,13 +23435,23 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
       </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV123" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23628,6 +23958,11 @@
       <c r="Q126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23640,13 +23975,23 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24153,6 +24498,11 @@
       <c r="Q129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24165,13 +24515,23 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
       </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV129" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25068,6 +25428,11 @@
       <c r="Q134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25080,13 +25445,23 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
       </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV134" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25593,6 +25968,11 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25605,13 +25985,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26118,6 +26508,11 @@
       <c r="Q140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26130,13 +26525,23 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
       </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV140" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26643,6 +27048,11 @@
       <c r="Q143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26655,13 +27065,23 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
       </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV143" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27168,6 +27588,11 @@
       <c r="Q146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27180,13 +27605,23 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27693,6 +28128,11 @@
       <c r="Q149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27705,13 +28145,23 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
       </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV149" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28218,6 +28668,11 @@
       <c r="Q152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28230,13 +28685,23 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
       </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV152" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28743,6 +29208,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28755,13 +29225,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29268,6 +29748,11 @@
       <c r="Q158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29280,13 +29765,23 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
       </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV158" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29793,6 +30288,11 @@
       <c r="Q161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29805,13 +30305,23 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
       </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV161" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30318,6 +30828,11 @@
       <c r="Q164" t="n">
         <v>0</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30330,13 +30845,23 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
       </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV164" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30843,6 +31368,11 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30855,12 +31385,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
